--- a/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,99</t>
+          <t>0,2; 4,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,34</t>
+          <t>-0,56; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,25</t>
+          <t>-3,24; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,62</t>
+          <t>-3,07; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 537,71</t>
+          <t>-3,67; 420,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 278,38</t>
+          <t>-21,23; 253,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 78,61</t>
+          <t>-71,29; 80,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 264,02</t>
+          <t>-45,66; 256,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,94</t>
+          <t>-1,27; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,37</t>
+          <t>-3,33; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,18</t>
+          <t>-2,8; 1,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -2,99</t>
+          <t>-11,84; -3,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 131,53</t>
+          <t>-44,76; 121,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 35,44</t>
+          <t>-55,39; 39,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 57,77</t>
+          <t>-66,62; 53,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,31; -41,15</t>
+          <t>-85,04; -39,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,83</t>
+          <t>-2,07; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,66</t>
+          <t>-0,94; 4,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,17</t>
+          <t>-1,8; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,12</t>
+          <t>-0,67; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 93,4</t>
+          <t>-37,62; 82,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 107,46</t>
+          <t>-14,97; 109,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 85,35</t>
+          <t>-38,67; 84,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 164,94</t>
+          <t>-14,79; 159,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,36</t>
+          <t>-0,28; 6,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,9</t>
+          <t>-0,11; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,23</t>
+          <t>-3,48; 2,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,84</t>
+          <t>-2,48; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 159,45</t>
+          <t>-5,94; 155,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 127,99</t>
+          <t>-1,4; 127,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 41,68</t>
+          <t>-38,78; 52,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 213,69</t>
+          <t>-23,62; 170,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,3</t>
+          <t>-5,18; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,42</t>
+          <t>-3,45; 4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 8,64</t>
+          <t>0,28; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -1,96</t>
+          <t>-9,26; -2,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 33,65</t>
+          <t>-45,56; 53,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 55,04</t>
+          <t>-26,7; 54,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 129,62</t>
+          <t>0,67; 117,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -14,24</t>
+          <t>-50,01; -17,51</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,48</t>
+          <t>-4,01; 4,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 3,26</t>
+          <t>-8,35; 2,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,85</t>
+          <t>-2,83; 5,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 63,49</t>
+          <t>-0,37; 61,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 71,27</t>
+          <t>-35,35; 68,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 31,93</t>
+          <t>-47,76; 27,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 84,76</t>
+          <t>-32,38; 93,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 559,78</t>
+          <t>-3,38; 570,24</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 5,74</t>
+          <t>-4,58; 6,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 10,51</t>
+          <t>-2,96; 10,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 11,84</t>
+          <t>1,93; 11,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 9,65</t>
+          <t>-0,64; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 67,3</t>
+          <t>-31,1; 73,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 90,62</t>
+          <t>-14,39; 95,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 211,73</t>
+          <t>18,14; 222,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 41,32</t>
+          <t>-2,21; 40,74</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,35</t>
+          <t>0,13; 2,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,02</t>
+          <t>0,31; 3,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,56</t>
+          <t>0,12; 2,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 21,24</t>
+          <t>-0,22; 21,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 53,59</t>
+          <t>2,07; 52,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 45,39</t>
+          <t>3,63; 47,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 51,15</t>
+          <t>1,35; 50,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 212,75</t>
+          <t>-2,36; 250,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,1</t>
+          <t>0,07; 4,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,29</t>
+          <t>-0,72; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,33</t>
+          <t>-3,05; 1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,82</t>
+          <t>-1,76; 7,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 420,34</t>
+          <t>-10,37; 531,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 253,4</t>
+          <t>-29,77; 273,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 80,93</t>
+          <t>-73,07; 88,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 256,96</t>
+          <t>-33,07; 308,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,61</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-68,66%</t>
+          <t>-53,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,89</t>
+          <t>-1,25; 2,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,42</t>
+          <t>-3,25; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,1</t>
+          <t>-2,71; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -3,12</t>
+          <t>-8,72; -0,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 121,52</t>
+          <t>-44,0; 127,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 39,32</t>
+          <t>-53,36; 45,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 53,87</t>
+          <t>-64,84; 51,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,04; -39,25</t>
+          <t>-74,69; -12,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,58</t>
+          <t>-2,03; 2,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,64</t>
+          <t>-0,77; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,35</t>
+          <t>-1,74; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,93</t>
+          <t>0,16; 4,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 82,28</t>
+          <t>-37,93; 105,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 109,25</t>
+          <t>-12,13; 110,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 84,09</t>
+          <t>-38,42; 93,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 159,21</t>
+          <t>2,14; 193,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>-7,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 6,11</t>
+          <t>0,05; 6,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,35</t>
+          <t>-0,18; 6,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,92</t>
+          <t>-3,61; 2,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,27</t>
+          <t>-3,74; 1,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 155,06</t>
+          <t>-1,34; 153,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 127,2</t>
+          <t>-5,13; 122,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 52,15</t>
+          <t>-40,04; 44,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 170,68</t>
+          <t>-30,8; 21,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-35,12%</t>
+          <t>-29,44%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,25</t>
+          <t>-5,05; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,93</t>
+          <t>-3,72; 5,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 8,17</t>
+          <t>0,12; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -2,43</t>
+          <t>-8,02; -1,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 53,4</t>
+          <t>-45,65; 48,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 54,82</t>
+          <t>-29,17; 56,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 117,93</t>
+          <t>-0,38; 123,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,01; -17,51</t>
+          <t>-45,06; -8,1</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,71</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>219,98%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,52</t>
+          <t>-4,37; 4,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 2,77</t>
+          <t>-8,32; 3,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,12</t>
+          <t>-3,41; 4,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 61,56</t>
+          <t>-2,42; 4,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 68,26</t>
+          <t>-39,25; 73,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 27,4</t>
+          <t>-47,66; 28,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 93,7</t>
+          <t>-35,12; 80,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 570,24</t>
+          <t>-15,35; 40,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,41</t>
+          <t>-4,85; 6,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 10,43</t>
+          <t>-2,92; 10,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,88</t>
+          <t>2,25; 12,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,72</t>
+          <t>-0,32; 10,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 73,72</t>
+          <t>-32,9; 67,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 95,18</t>
+          <t>-14,75; 93,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,14; 222,91</t>
+          <t>21,01; 227,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 40,74</t>
+          <t>-1,12; 43,39</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,4</t>
+          <t>0,04; 2,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,19</t>
+          <t>0,51; 3,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,6</t>
+          <t>0,18; 2,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 21,97</t>
+          <t>-0,95; 1,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 52,83</t>
+          <t>0,69; 54,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 47,04</t>
+          <t>6,25; 48,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 50,72</t>
+          <t>3,05; 51,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 250,37</t>
+          <t>-8,17; 18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
